--- a/reports/一级子公司A_利润表_2026-05.xlsx
+++ b/reports/一级子公司A_利润表_2026-05.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>181982726</v>
+        <v>186034422</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>177337977</v>
+        <v>177385829</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>798264946</v>
+        <v>798064774</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>723101</v>
+        <v>720301</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3355647</v>
+        <v>3362106</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>625208</v>
+        <v>623765</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2909380</v>
+        <v>2915832</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>529446</v>
+        <v>527911</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2466749</v>
+        <v>2469240</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>488860</v>
+        <v>485427</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2270660</v>
+        <v>2269675</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>265569</v>
+        <v>263932</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1233258</v>
+        <v>1232353</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>211712</v>
+        <v>211417</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>986270</v>
+        <v>985122</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>179138830</v>
+        <v>183201669</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>174494081</v>
+        <v>174553076</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>89643090</v>
+        <v>89738465</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>392154257</v>
+        <v>391308380</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1642249</v>
+        <v>1650639</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>7646215</v>
+        <v>7634326</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1486890</v>
+        <v>1492988</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6910885</v>
+        <v>6904463</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>79943203</v>
+        <v>79896276</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>370087846</v>
+        <v>370681892</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1692076</v>
+        <v>1702311</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>7886169</v>
+        <v>7909375</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>741143</v>
+        <v>743862</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3454122</v>
+        <v>3460900</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2663687</v>
+        <v>2647323</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>12346272</v>
+        <v>12361521</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1167888</v>
+        <v>1164604</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>5425395</v>
+        <v>5438243</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4550491</v>
+        <v>4544882</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>21206116</v>
+        <v>21248720</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>94258</v>
+        <v>92239</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>452907</v>
+        <v>463952</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2406196</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>11246049</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1605276</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>7490720</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>121376472</v>
+        <v>130036392</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>108503915</v>
+        <v>108458925</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>106281034</v>
+        <v>106224300</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>493321942</v>
+        <v>492302279</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2222881</v>
+        <v>2234625</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>10355256</v>
+        <v>10341735</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>4050160</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>18728246</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1296835</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5998421</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>810265</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3752482</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>971171</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4506536</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>727038</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3381647</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>483636</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2254772</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>402170</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1878528</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1852977</v>
+        <v>1848850</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>8634542</v>
+        <v>8645830</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1435724</v>
+        <v>1424892</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>6664542</v>
+        <v>6664112</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1168200</v>
+        <v>1160908</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>5425691</v>
+        <v>5425300</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8781870</v>
+        <v>8766588</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>40929575</v>
+        <v>40900227</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>366631</v>
+        <v>370204</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1759991</v>
+        <v>1723628</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>702879</v>
+        <v>689642</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3376126</v>
+        <v>3443172</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>794534</v>
+        <v>689642</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3825171</v>
+        <v>3443172</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>94023</v>
+        <v>93008</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>452605</v>
+        <v>462638</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>353944</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1759262</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>709215</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3280797</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>235973</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1174934</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>176753</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>881909</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>294027</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1470665</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1007278</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4697398</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>156142</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>784374</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>116916</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>587968</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>194689</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>979169</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>136287</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>684791</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>97440</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>488708</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>78083</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>390701</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>58687</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>292919</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>57762358</v>
+        <v>55625011</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>66871581</v>
+        <v>62266320</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>405117</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1873251</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>98365</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>489168</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>156566</v>
+        <v>155229</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>755008</v>
+        <v>773061</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>57605792</v>
+        <v>55874899</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5557460</v>
+        <v>5466383</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>26690274</v>
+        <v>27350486</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>52048332</v>
+        <v>50408516</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>52048332</v>
+        <v>50408516</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>52048332</v>
+        <v>50408516</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>52048332</v>
+        <v>50408516</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>52048332</v>
+        <v>50408516</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
